--- a/Test/Test Suite/TestPlanPrincipleStrategy.xlsx
+++ b/Test/Test Suite/TestPlanPrincipleStrategy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="2328" windowWidth="17280" windowHeight="9420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,14 +14,14 @@
     <sheet name="CombatContext" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -38,27 +38,11 @@
     </font>
     <font>
       <name val="TH Sarabun New"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="TH Sarabun New"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="TH Sarabun New"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -81,7 +65,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -106,14 +90,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -121,78 +107,56 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -200,172 +164,83 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -763,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="21.77734375" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -771,7 +646,9 @@
     <col width="18.109375" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="8.88671875" customWidth="1" style="2" min="4" max="5"/>
     <col width="22" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="8.88671875" customWidth="1" style="2" min="7" max="16384"/>
+    <col width="26.21875" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="8.88671875" customWidth="1" style="2" min="8" max="8"/>
+    <col width="8.88671875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,215 +676,283 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SystemUnderTest</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>FunctionUnderTest</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>No of Test Cases</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Relative Defects (ID)</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Line Coverage (%)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>KongmingCombatStrategy</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>canSurviveDestruction</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
+      <c r="D6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>KongmingCombatStrategy</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>calculateKills (inherited)</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
+      <c r="D7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="26" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>StandardCombatStrategy</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>calculateKills</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
+      <c r="D8" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>StandardCombatStrategy</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>canSurviveDestruction</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
+      <c r="D9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="26" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>constructor / executeSurvival</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="29" t="n"/>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
+      <c r="D10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>constructor / executeKills</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29" t="n"/>
+      <c r="D11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>constructor</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
+      <c r="D12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>executeKills</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
+      <c r="D13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>MarshalAbilityContext</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
+      <c r="D14" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="29" t="n">
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
+      <c r="D15" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="25" t="n">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G8:G9"/>
     <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1025,11 +970,11 @@
   <cols>
     <col width="4.33203125" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="9.88671875" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="12.77734375" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
-    <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="30" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="52" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="60" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,211 +1081,234 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A3:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="3" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="40" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="84" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>KongmingCombatStrategy</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="40" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="15" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="40" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="19" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="40" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="15" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>None (real object); statistical runs</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="40" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="15" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>canSurviveDestruction</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>run canSurviveDestruction() 10,000 times, count survivals</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>survival rate between 0.45 and 0.55 (~50%)</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="33" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>survival rate over 10,000 rolls stayed inside the 0.45-0.55 band on every run (the exact count differs per run because the roll is random)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>canSurviveDestruction</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>single call, repeated 200 times</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>returns both true and false at least once (never a constant)</t>
         </is>
       </c>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>within 200 rolls both true and false occurred, so the override is not stuck on one value</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>calculateKills (inherited)</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(attackKillRatio 3.5), soldiers 100</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>kills == 350 - Kongming inherits StandardCombatStrategy so only survival differs</t>
         </is>
       </c>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="33" t="n"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>calculateKills(player with ratio 3.5, 100) == 350 and equals StandardCombatStrategy.calculateKills for the same input</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1361,336 +1329,399 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A3:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="3" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="40" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="84" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>MarshalAbilityContext</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="40" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="15" t="n"/>
     </row>
     <row r="5" ht="35.4" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="40" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="19" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="40" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="15" t="n"/>
     </row>
     <row r="7" ht="35.4" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>None (real Player/Marshal objects)</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="40" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="15" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Player with marshal = null</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>StandardMarshalStrategy</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="33" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>StandardMarshalStrategy returned for a player with marshal == null</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'NO_ACCIDENT')</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>NoAccidentStrategy; preventsAccidents() true; getRecruitFoodMultiplier() 1.25</t>
         </is>
       </c>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>NoAccidentStrategy; preventsAccidents() true and getRecruitFoodMultiplier() 1.25</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'REBELLION')</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>RebellionStrategy; causesRebellions() true</t>
         </is>
       </c>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="33" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>RebellionStrategy; causesRebellions() true</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'UNKNOWN_FOO')</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>StandardMarshalStrategy (getOrDefault fallback)</t>
         </is>
       </c>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>StandardMarshalStrategy for the unknown key 'UNKNOWN_FOO' (getOrDefault fallback)</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'FASTER_TRAVEL')</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>FasterTravelStrategy; travelsFaster() true; other flags false; multiplier 1.0</t>
         </is>
       </c>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="33" t="n"/>
-      <c r="G16" s="33" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>FasterTravelStrategy; travelsFaster() true while preventsAccidents, causesRebellions and survivesDestruction are false and the multiplier is 1.0</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TC06</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C17" s="36" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'SURVIVE_DESTRUCTION')</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>SurviveDestructionStrategy; survivesDestruction() true</t>
         </is>
       </c>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="33" t="n"/>
-      <c r="G17" s="33" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>SurviveDestructionStrategy; survivesDestruction() true</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>TC07</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C18" s="36" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType = null)</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>StandardMarshalStrategy (null check before the map lookup)</t>
         </is>
       </c>
-      <c r="E18" s="33" t="n"/>
-      <c r="F18" s="33" t="n"/>
-      <c r="G18" s="33" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>StandardMarshalStrategy when specialAbilityType is null</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>TC08</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>getStrategy</t>
         </is>
       </c>
-      <c r="C19" s="36" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal('NO_ACCIDENT')</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>travelsFaster() false and causesRebellions() false - NoAccidentStrategy only overrides those two</t>
         </is>
       </c>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="33" t="n"/>
-      <c r="G19" s="33" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>travelsFaster() false and causesRebellions() false on NoAccidentStrategy</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1711,261 +1742,300 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A3:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="3" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="40" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>StandardCombatStrategy</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="40" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="40" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="21" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="40" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>None (real objects built with Player.builder / Marshal.builder)</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="40" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="15" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>calculateKills</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Player(marshal = null), soldiers 100</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>100 (ratio defaults to 1.0)</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="33" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>100 kills for 100 soldiers when the player has no marshal (ratio defaults to 1.0)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>calculateKills</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Player(marshal.attackKillRatio = -1), soldiers 100</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>0 - Math.max(0, floor(-100)) clamps negatives</t>
         </is>
       </c>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>0 kills with ratio -1.0: Math.max(0, floor(-100)) clamps the negative</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>calculateKills</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Player(marshal.attackKillRatio = 3.5), soldiers 100</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="33" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>350 kills with ratio 3.5 on 100 soldiers</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>calculateKills</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Player(marshal.attackKillRatio = 0.5), soldiers 15</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>7 - floor(7.5)</t>
         </is>
       </c>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>7 kills with ratio 0.5 on 15 soldiers (floor of 7.5)</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TC05</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>canSurviveDestruction</t>
         </is>
       </c>
-      <c r="C16" s="36" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>any Player</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>false always</t>
         </is>
       </c>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="33" t="n"/>
-      <c r="G16" s="33" t="n"/>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>canSurviveDestruction() false on three consecutive calls</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1986,236 +2056,267 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A3:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="3" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Eternal Crash2</t>
         </is>
       </c>
-      <c r="C3" s="41" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="41" t="n"/>
-      <c r="F3" s="41" t="n"/>
-      <c r="G3" s="40" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
+      <c r="G3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>SystemUnderTest/Class under Test</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>CombatContext</t>
         </is>
       </c>
-      <c r="C4" s="41" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="41" t="n"/>
-      <c r="F4" s="41" t="n"/>
-      <c r="G4" s="40" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Window 11, java version "1.8.0_503" , Junit 5</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="41" t="n"/>
-      <c r="F5" s="41" t="n"/>
-      <c r="G5" s="40" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Window 11, java version "17.0.12" , Junit 5</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+      <c r="G5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="21" t="n">
         <v>46305</v>
       </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="41" t="n"/>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="40" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>None (real Player/Marshal objects)</t>
         </is>
       </c>
-      <c r="C7" s="41" t="n"/>
-      <c r="D7" s="41" t="n"/>
-      <c r="E7" s="41" t="n"/>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="40" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="15" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>TestCaseID</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Function Under Test</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>TestData</t>
         </is>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>DefectID</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TC01</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>constructor / executeSurvival</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'SURVIVE_DESTRUCTION')</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>strategy is KongmingCombatStrategy</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="33" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>strategy resolves to KongmingCombatStrategy for SURVIVE_DESTRUCTION and executeSurvival() returned true at least once across repeated rolls</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>TC02</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>constructor / executeKills</t>
         </is>
       </c>
-      <c r="C13" s="36" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(specialAbilityType 'NO_ACCIDENT')</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>falls back to StandardCombatStrategy (only SURVIVE_DESTRUCTION is registered)</t>
         </is>
       </c>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>NO_ACCIDENT is not registered, so the context falls back to StandardCombatStrategy: executeSurvival() never true and executeKills(100) == 100</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TC03</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>constructor</t>
         </is>
       </c>
-      <c r="C14" s="36" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Player(marshal = null)</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>StandardCombatStrategy</t>
         </is>
       </c>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="33" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>marshal == null gives StandardCombatStrategy: executeSurvival() false, executeKills(100) == 100</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TC04</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>executeKills</t>
         </is>
       </c>
-      <c r="C15" s="36" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Player with Marshal(attackKillRatio 2.0), soldiers 40</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>executeKills(40) == 80 with marshal ratio 2.0</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
